--- a/AutoRappel_Emmaus-Connect-main/test/Rappels pour participants lendemain-2023-11-30-12-12-59.xlsx
+++ b/AutoRappel_Emmaus-Connect-main/test/Rappels pour participants lendemain-2023-11-30-12-12-59.xlsx
@@ -803,7 +803,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:Z57"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="4.328125" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
@@ -1108,6 +1108,9 @@
       </c>
       <c r="L13" s="13" t="inlineStr"/>
       <c r="M13" s="8" t="n"/>
+      <c r="Z13" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n"/>
@@ -1145,9 +1148,6 @@
       </c>
       <c r="L14" s="13" t="inlineStr"/>
       <c r="M14" s="8" t="n"/>
-      <c r="Z14" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n"/>
@@ -1185,9 +1185,6 @@
       </c>
       <c r="L15" s="13" t="inlineStr"/>
       <c r="M15" s="8" t="n"/>
-      <c r="Z15" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n"/>
